--- a/artfynd/A 21594-2025 artfynd.xlsx
+++ b/artfynd/A 21594-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117192089</v>
+        <v>117192092</v>
       </c>
       <c r="B2" t="n">
-        <v>77830</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594387</v>
+        <v>594757</v>
       </c>
       <c r="R2" t="n">
-        <v>6972129</v>
+        <v>6971675</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117192087</v>
+        <v>117192089</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594389</v>
+        <v>594387</v>
       </c>
       <c r="R3" t="n">
-        <v>6972133</v>
+        <v>6972129</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117192088</v>
+        <v>117192091</v>
       </c>
       <c r="B4" t="n">
-        <v>77378</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594385</v>
+        <v>594757</v>
       </c>
       <c r="R4" t="n">
-        <v>6972150</v>
+        <v>6971679</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117192091</v>
+        <v>117192088</v>
       </c>
       <c r="B5" t="n">
-        <v>77830</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594757</v>
+        <v>594385</v>
       </c>
       <c r="R5" t="n">
-        <v>6971679</v>
+        <v>6972150</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,12 +1066,7 @@
         <v>117192090</v>
       </c>
       <c r="B6" t="n">
-        <v>78183</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,6 +1157,219 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>117192087</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Anderberghöjden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>594389</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6972133</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>117307903</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78740</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6332580</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Calicium ramboldiicola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Tibell et al.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Anderberghöjden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>594389</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6972133</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Parasit på vedflamlav.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>vedflamlav</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21594-2025 artfynd.xlsx
+++ b/artfynd/A 21594-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192092</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192089</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192091</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192088</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192090</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192087</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1370,8 +1405,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117307903</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>